--- a/output/processing/214-215_Sistema_433MHz_RC.xlsx
+++ b/output/processing/214-215_Sistema_433MHz_RC.xlsx
@@ -527,19 +527,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
@@ -649,11 +649,301 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>XR2N 433-868</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>12 ÷ 24 V~ - 12 ÷ 24 V~</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>90 x 70 x 32,5 mm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>IP 44</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-20° C ÷ +55 ° C</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>XR4N 433-868</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
